--- a/output/graficos_nacionales/plot_nacional_m_movinterna_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_m_movinterna_a_2021.xlsx
@@ -16233,7 +16233,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Movilidad interna (CMI)</t>
+          <t>Por comunas</t>
         </is>
       </c>
     </row>

--- a/output/graficos_nacionales/plot_nacional_m_movinterna_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_m_movinterna_a_2021.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="731">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="734">
   <si>
     <t xml:space="preserve">year</t>
   </si>
@@ -2173,7 +2173,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 22:22</t>
+    <t xml:space="preserve">2026-07-30 15:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2185,16 +2185,25 @@
     <t xml:space="preserve">Imagen asociada</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">plot_nacional_m_movinterna_a_2021.png</t>
   </si>
   <si>
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
+    <t xml:space="preserve">Movilidad interna (CMI)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
+    <t xml:space="preserve">Comuna (vista nacional macrozonal)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Año</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021</t>
   </si>
   <si>
     <t xml:space="preserve">variable</t>
@@ -13647,23 +13656,23 @@
         <v>723</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
     </row>
   </sheetData>
@@ -13685,21 +13694,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>15</v>
@@ -13708,7 +13717,7 @@
         <v>2021</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_nacionales/plot_nacional_m_movinterna_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_m_movinterna_a_2021.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Macrozona Austral</t>
   </si>
   <si>
-    <t xml:space="preserve">value</t>
+    <t xml:space="preserve">Valor (por 1.000)</t>
   </si>
   <si>
     <t xml:space="preserve">12303</t>
@@ -769,16 +769,22 @@
     <t xml:space="preserve">Pumanque</t>
   </si>
   <si>
+    <t xml:space="preserve">13122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peñalolén</t>
+  </si>
+  <si>
     <t xml:space="preserve">7407</t>
   </si>
   <si>
     <t xml:space="preserve">Villa Alegre</t>
   </si>
   <si>
-    <t xml:space="preserve">13122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peñalolén</t>
+    <t xml:space="preserve">13115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lo Barnechea</t>
   </si>
   <si>
     <t xml:space="preserve">16203</t>
@@ -787,12 +793,6 @@
     <t xml:space="preserve">Coelemu</t>
   </si>
   <si>
-    <t xml:space="preserve">13115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lo Barnechea</t>
-  </si>
-  <si>
     <t xml:space="preserve">13404</t>
   </si>
   <si>
@@ -1600,18 +1600,18 @@
     <t xml:space="preserve">Hualpén</t>
   </si>
   <si>
+    <t xml:space="preserve">8104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Florida</t>
+  </si>
+  <si>
     <t xml:space="preserve">9121</t>
   </si>
   <si>
     <t xml:space="preserve">Cholchol</t>
   </si>
   <si>
-    <t xml:space="preserve">8104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Florida</t>
-  </si>
-  <si>
     <t xml:space="preserve">14102</t>
   </si>
   <si>
@@ -1828,18 +1828,18 @@
     <t xml:space="preserve">Quilleco</t>
   </si>
   <si>
+    <t xml:space="preserve">14202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Futrono</t>
+  </si>
+  <si>
     <t xml:space="preserve">10108</t>
   </si>
   <si>
     <t xml:space="preserve">Maullín</t>
   </si>
   <si>
-    <t xml:space="preserve">14202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Futrono</t>
-  </si>
-  <si>
     <t xml:space="preserve">10104</t>
   </si>
   <si>
@@ -1963,18 +1963,18 @@
     <t xml:space="preserve">Queilén</t>
   </si>
   <si>
+    <t xml:space="preserve">8106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lota</t>
+  </si>
+  <si>
     <t xml:space="preserve">9203</t>
   </si>
   <si>
     <t xml:space="preserve">Curacautín</t>
   </si>
   <si>
-    <t xml:space="preserve">8106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lota</t>
-  </si>
-  <si>
     <t xml:space="preserve">9108</t>
   </si>
   <si>
@@ -2173,7 +2173,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:30</t>
+    <t xml:space="preserve">2026-09-08 10:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2590,9 +2590,9 @@
     <col min="5" max="5" width="22.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="19.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="12.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="19.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="10.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="14.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="19.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6312,10 +6312,10 @@
         <v>2021</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>108</v>
+        <v>60</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>250</v>
@@ -6344,10 +6344,10 @@
         <v>2021</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>252</v>
@@ -6376,10 +6376,10 @@
         <v>2021</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>254</v>
@@ -6408,10 +6408,10 @@
         <v>2021</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>256</v>
@@ -10568,10 +10568,10 @@
         <v>2021</v>
       </c>
       <c r="B250" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="D250" s="2" t="s">
         <v>527</v>
@@ -10600,10 +10600,10 @@
         <v>2021</v>
       </c>
       <c r="B251" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="D251" s="2" t="s">
         <v>529</v>
@@ -11784,10 +11784,10 @@
         <v>2021</v>
       </c>
       <c r="B288" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="D288" s="2" t="s">
         <v>603</v>
@@ -11816,10 +11816,10 @@
         <v>2021</v>
       </c>
       <c r="B289" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="D289" s="2" t="s">
         <v>605</v>
@@ -12520,10 +12520,10 @@
         <v>2021</v>
       </c>
       <c r="B311" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="D311" s="2" t="s">
         <v>648</v>
@@ -12552,10 +12552,10 @@
         <v>2021</v>
       </c>
       <c r="B312" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="D312" s="2" t="s">
         <v>650</v>
@@ -13687,7 +13687,7 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="16.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="19.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="13.71" hidden="0" customWidth="1"/>
   </cols>
